--- a/src/attributions/attributions_ig_traj_214.xlsx
+++ b/src/attributions/attributions_ig_traj_214.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,22 +999,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.07498804478836586</v>
+        <v>0.07751500535089602</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2123108505157703</v>
+        <v>0.06019406362478211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005516432524130028</v>
+        <v>-0.02964945639522543</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1023,79 +1023,79 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0210650617049058</v>
+        <v>-0.02473083272128246</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2062088150060369</v>
+        <v>-0.04127108106985779</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.007387703804133994</v>
+        <v>0.01972218979490549</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.09179633776493132</v>
+        <v>0.04269477555603922</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01626758625129003</v>
+        <v>-0.1049822437184173</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.03827681932504355</v>
+        <v>0.03679522535616413</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.05304819134633224</v>
+        <v>0.0281829621626174</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01596718197831162</v>
+        <v>-0.03414760918842565</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.001357506954384982</v>
+        <v>-0.02108303543017395</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
@@ -1104,55 +1104,55 @@
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03337734227611048</v>
+        <v>0.1465267003142251</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.02710235950979624</v>
+        <v>-0.02730974889273364</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.06807114299100285</v>
+        <v>0.2300218729008797</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1493238582359526</v>
+        <v>0.2661893512918467</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.07989574898010814</v>
+        <v>-0.01195577597917663</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.004724416540976223</v>
+        <v>0.03185310591127914</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1164,16 +1164,16 @@
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01731206187656933</v>
+        <v>-0.05309764085117058</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.08423891762249715</v>
+        <v>0.02728848978685907</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03181235655624312</v>
+        <v>-0.07946028780905164</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,58 +1182,58 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03624722305829137</v>
+        <v>-0.07891710494447232</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.03913293478256753</v>
+        <v>-0.105051960725081</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.08637971709137597</v>
+        <v>-0.006794161304261241</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.04500391369559421</v>
+        <v>0.106537726323913</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01500758071599884</v>
+        <v>-0.1070882443355774</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02086773070508119</v>
+        <v>0.01085030964627803</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1245,73 +1245,73 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03220467152992416</v>
+        <v>-0.1257671565512366</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.03364726260395302</v>
+        <v>-0.03068416664032776</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01645725400885414</v>
+        <v>-0.03374081557697885</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01104918755697818</v>
+        <v>-0.09327946270572388</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02074356515685865</v>
+        <v>0.1195036971867391</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.03582172844414858</v>
+        <v>-0.01246346643639806</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04603546316646197</v>
+        <v>-0.1234142815890354</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.03621017246313984</v>
+        <v>-0.02396368197124307</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.009757611166591691</v>
+        <v>-0.01307526456156267</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1320,22 +1320,22 @@
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.02952187127600957</v>
+        <v>-0.06888308893770582</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.02516906389234852</v>
+        <v>0.05930426085440794</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03783215140409813</v>
+        <v>-0.008303174381905601</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
@@ -1344,28 +1344,28 @@
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01844302020456456</v>
+        <v>-0.01892280253805329</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.03409103206182655</v>
+        <v>0.01785533966729666</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.01622991875651391</v>
+        <v>0.002317497469410392</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,52 +1377,52 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.0547282908726129</v>
+        <v>0.07246531077524175</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.01156697219937911</v>
+        <v>0.1157890065992518</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02323154868926323</v>
+        <v>0.2052697304464707</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04188967657062639</v>
+        <v>-0.1038115540129545</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.07034029962704759</v>
+        <v>0.1763366169362517</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.02720351628130804</v>
+        <v>0.01478271289326148</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04467283160219787</v>
+        <v>-0.06627438081108325</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.0332712947545084</v>
+        <v>0.02813911211500303</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03374213308970007</v>
+        <v>-0.002963484893878177</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1452,52 +1452,52 @@
         <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04336569382910841</v>
+        <v>-0.1532497714650022</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.02930277627662451</v>
+        <v>-0.004182638579556764</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01670699430381313</v>
+        <v>-0.03161750349483168</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.003066748497303185</v>
+        <v>-0.1033617751536028</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.006813118420519349</v>
+        <v>-0.03412848319353672</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.006099503072460796</v>
+        <v>0.07673036644865798</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1506,58 +1506,58 @@
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01240537822611858</v>
+        <v>-0.1434697124940549</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.02042875914825069</v>
+        <v>0.1833265600476569</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.007039864533620131</v>
+        <v>-0.01269999504635618</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03029568608595597</v>
+        <v>-0.06226022605136879</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.03483274327951914</v>
+        <v>0.0002590587736194077</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,25 +1568,25 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.02000566049328851</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.01095542009506842</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.01455435211310706</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1595,64 +1595,64 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.002631092807478951</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0.001382071028009926</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.005002371845475102</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.01992200897878825</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.0155846764666184</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.01374482037160375</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.002212822624772454</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1661,94 +1661,94 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.01654269506241926</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.01742120490726687</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.00675117057640488</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.03088372971223993</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.004778916718029256</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.01406870069390822</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.03629408117925925</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.01333788281623472</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.01119534590461186</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.01577185530001061</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0.007204448589107563</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,88 +1757,88 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.02960205548151455</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.01858033651741887</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.0008816849785281645</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.002522075662729096</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.02265423419278405</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.007302061935889431</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.01394280303039043</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.01884485840685256</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.00852783782964512</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.001873315185704743</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.02949894159451544</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.007462285658178656</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.01100665520821281</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.02378500591630921</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.011707256156601</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.001527250000470184</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -1904,49 +1904,49 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.0185019155543172</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.002485983822881697</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0.005515247288365892</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.01908194609039693</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.005283960229539942</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.003943650741242997</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
@@ -1955,52 +1955,52 @@
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>-0.001799836431963992</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.02227996957114436</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.01782555798683784</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.017758775209514</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.005908108925413002</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.01295400894975667</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.02222051892406428</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0.0008653434569626485</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.01534946066149045</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2039,52 +2039,52 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.02758432842193551</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.01334509126897806</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.02355727882793508</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>-0.01058693559824982</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.001360896441572844</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0.0009489625075333665</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,45 +2093,8580 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.01431048701219947</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.008291630885449425</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.008872281574906129</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01327817036849759</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3057523227460114</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06579167629790363</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.2601915802061966</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02968277776807611</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.005423304434093882</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04831272363754007</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1222037196172892</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.09282947229337751</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1350358918814083</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.119718367081547</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05716150181979567</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1472858053044284</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.120955653445357</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.05564058727457193</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.2355049025935752</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.6427071852819255</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.2523550040367366</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.4216575468079953</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.1128562629496318</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.06564242316416113</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1645604742129381</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.06596592720487399</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.08780911047235011</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1642245428998055</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2162555667136201</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.102726014258895</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.2776585600512539</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2562667729184678</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.06093926397851217</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1766194307047158</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.233475686560081</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.05658685757637985</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.143933765759135</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.2446523429804898</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.05575568320706113</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1517969809323543</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.1324954261874808</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.05048531141379477</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.1371458580937623</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.08674429709316184</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.007552348485462051</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.07261903360331157</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.159260147069458</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.04484137452983293</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1673148913369745</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.1198412885971141</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.0864650391803147</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.153367871689946</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.1693119702494127</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.1895854796273398</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.1621745883383629</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.2347041410654898</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.1166271024937341</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1609001969343876</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-0.1241926100016105</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>-0.07009745179052719</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.2878688561545821</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>-0.008678678164605866</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.06419936475337053</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.05834805540727327</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.1165236057022418</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.1928152609455519</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3723447833601671</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03270131570441095</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.1481132587545465</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.07806574086418649</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.0123789304044336</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.0474207524753178</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1531175198803662</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1393495340047074</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.03251322459877232</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.02668232532783662</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.2318199362577361</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.03641095460051185</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2001752736061113</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1517265925466987</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.14776295440619</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.7523265048028468</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.2236557542142625</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.1946416528082396</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.02013384261836163</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.07032665556398773</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1123049925139021</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.03469309981712113</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.1329383957358534</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.157470095687143</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.3829288205992971</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.02554702847301625</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.2462874241705843</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.2470015968941225</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.03765293856164183</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1688854066205257</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.1605812045751217</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.0877320112976422</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.0004823473311048004</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.2229940873196077</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.0318494895672547</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.1684761980209558</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.0382963263445471</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.07715113876007045</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.0391536105044364</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.1060452160158828</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.002280503920621933</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.0101241945769894</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.09279946202944754</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.07920632051252594</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.1261248261701846</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.05020222813408409</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.1450857324674949</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.08032194995051321</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.1307088247943847</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.2127589826205118</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.03934420998924418</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.2461501097544718</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.07529357539274659</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1444772395630748</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.2097378547464279</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.07689302414421577</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.2473284011354092</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0.02881714120084175</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.0008173531966460252</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.1080102913238926</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.09812784982167637</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.1019689153658571</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.3778613044784142</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02849207907819654</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.1836100948352341</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1455419169676797</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.01419360066480611</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.07765334978164609</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1180120793323559</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.151815996269272</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0286213852713408</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.05242708817068826</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.2346623093466465</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.08678582768483063</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1676093115223271</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1079944240206459</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1103329200769282</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.6652669174793525</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.1650130555279703</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.1918088033585739</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.005390590819121107</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.03662852657117052</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.1576517212884833</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.04910847126916346</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.08784564411504185</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.05081774320523187</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.3173876833650052</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.0396185754647539</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.1429860922838909</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.2230112104191768</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.03824753962087318</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1375414661742255</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.133468630610159</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.04810326481924673</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.007859435166270499</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.2045450286298391</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.0352503407690993</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1461433650845621</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.05932880938322233</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.04206817422686795</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.03767508732298684</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.1202276270456558</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.01570233707490479</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.06758872960097351</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.02613499014974608</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.09186621841830427</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.1407803128045796</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.04287318118774365</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.08342510944347767</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.05427385247179062</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.1114991590851256</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.08860508754012039</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.07296839794279883</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.2268161139609564</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.05892538329875015</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1276088596143859</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.2431237035835043</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.07942028805398021</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.2388403238926852</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.0343818719065719</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>-0.006156833086654549</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.136569411252558</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.04978062805638354</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.02158113824724713</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5915928228725817</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.02703904971993809</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.08599319928904407</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.237825335095307</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4477958636757286</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.115732078472011</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.02416591850882351</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.09670599751248868</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1672337308926944</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1730801486147821</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.1562992695118425</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.006167786015266592</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.1326823582750994</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.3583078217787987</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.232765192223638</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.1208615506671584</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2796811097213507</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.1420132545468101</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.1855140622374054</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1993903488538412</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.864545694427319</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.009316265426709647</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1689379298351239</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1561617112762206</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.01679503937030948</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.1072122271818247</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.125129144069843</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.2593369916515429</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.04420871583938941</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.003950810730606918</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.1409970762303681</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.01292197288663296</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.401924531779132</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.09813528066541953</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.003017374006007177</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.1821313840544908</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.2894894678529111</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.05270337809803905</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.07350026865210699</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.129299637004917</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.2036905910701229</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1596578862146527</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.0184589665216395</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0973130588115652</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.2651658720770109</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.06204277344703473</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.08647788939643147</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.1277375875281912</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.04667460133478842</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>-0.01751025877837298</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.4670989354918933</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.02414726860203964</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.1022234194423413</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.05996840912381157</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.1070851832848327</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.1413922389906969</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.1552462539458248</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.07858529855686996</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0.01287561130452411</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0.01919168053910613</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.1240083848895802</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.08235209679429548</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.1113750297866926</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>-0.03174695355072726</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.1218329449272588</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0.06315923786977995</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.08506621150886014</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.2533118520349926</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.3035134126702108</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.06174690611041216</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.1258363676875327</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.1005455295567257</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.2252209711266066</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.1450059309370776</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.05643216118085478</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.3725972217875037</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1987113304785901</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.2872777944503768</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.001955805748718278</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.09628168885746909</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.1150369726107396</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0.1620036778414712</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.07776944272891266</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.2221806683100062</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.00889114524676057</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2071219026413123</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.08877588718342412</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.04478604186745562</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1286645198798842</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.08966617172079253</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.008144594579350361</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.03370216851146943</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.06395419421672134</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1431213228712825</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.03843540805456153</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1195672020171534</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.08110743673424843</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1499306681790015</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2996360635293902</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.06957098589022027</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1315384260110089</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.1029697910086837</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.2152339857655745</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.122901684707437</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.0289832139913838</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.0555476991848121</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.0558477689995262</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.2176631160389566</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.006294189550604892</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.08621590065375564</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.1294020485609261</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.01003754115683648</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.08062827819193177</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.0754060753117639</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1454528902636138</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.03863716173996184</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1215560049042346</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.005699454326810917</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.07379426942348548</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.004458481497502783</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.05275108982827627</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.007808168251972187</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.01254057254252931</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.01051363869718424</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.03530514319996934</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.04886435877787023</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.06151491881858998</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.02188798943999884</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.06679027795536686</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.01562047184399274</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>-0.009264715892268242</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.1033089678227893</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.07747313116232407</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.0943310659010813</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1354671311481852</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.0002291822268167367</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.06437560627687069</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1204245175631809</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.02566196495603158</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.1077820240306862</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.1063617964989911</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.008717879857046541</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.06736844530401781</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.1135241997632618</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.02004907915461063</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5426926885220239</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0216439644609442</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2923418538645213</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5661190309108086</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.09563749562748579</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1732764805130526</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1397605311519744</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.01367648753741331</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1497068214381005</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.003526613107522172</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.06849181379340162</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.09935494307920836</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1727523325470297</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.06534458083560532</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.09377243243483918</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.7312310865990951</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2731384405480271</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.2909331629523529</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.1745625232477025</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.005786022652157777</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.07462255900810361</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.01556386561530482</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.07798829561103375</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.05339409097859832</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.4500287478261169</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.01561094248927397</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.1659425329872808</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.2468026572995994</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.01019721401887829</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.1116319612636757</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.08906866487965028</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.08918441836054587</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.03077762234635981</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.2337639456815072</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.01062951206723477</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.1272685362638746</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.01319594562448032</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.01862450382195774</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.1003835515782636</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.07802572974572441</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.006917124975122394</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.09378093681377034</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.1401538117322314</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.0645073818154584</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.1251596216932681</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.141545844024727</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.0573144815104106</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.03738375968993004</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.1093431111161352</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.01044666176605473</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.03806871826453082</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2680743063443463</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.01515814202184137</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.1231524119663395</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.140885186080247</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.03966369495935109</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1121332542661675</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.2392300522857213</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.07504610062722977</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.006788029017868638</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1129876723369952</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.07090851134440188</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.3902375468267102</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1878473641023177</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.08867952594288413</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.4286505831184733</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2669801854041424</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1405202464332765</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.04109162553456438</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01533178623558822</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.0116301129691597</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.03030981253780318</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.153763654368942</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2217726761944828</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1440833969953473</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.04284552320016726</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.2331040469144822</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.2425030489364495</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.181064099648297</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.04343781030329023</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.03074010019572927</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.01945866673344017</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.09399341976463066</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1097310862730086</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.07264371408636869</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.01118954949787514</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.1862108689479959</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.08266163169074263</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.0009322462403479262</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.1947108411207845</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.06887845048790521</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.01049244579751373</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.09077372166627176</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0.08014811475072159</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.02544203126988138</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.2097527983783143</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.0736227543940539</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.0364095225089445</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1500866290529764</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.0391471973239022</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.0004639762198912587</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.09944575259077537</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0.07080232137162867</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.04003092691685088</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.04319991691164538</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.02552862267756187</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.003611966123300141</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.2200148816607372</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.0515402049540205</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.04497360168235492</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.1175512243664153</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0.01124282473495074</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.01338937614481888</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.2340009828994381</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0.0846230944567089</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.007484793920215041</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.08649804043931243</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.09156880849337438</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.02003220934353154</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.1824214370626203</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.01471591573657509</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.08443438783763341</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.1962122176105751</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0.005883491887675817</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3673263660664046</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.03132362115763966</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1574310961824845</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4485034714310024</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.130178196493785</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1955038102499164</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1181387580374067</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1505967697670783</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.008656607559602366</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.03162450802245122</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.2887825223557907</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.003527479040623809</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.04767021123248868</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.05554508401760289</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.01816034171727798</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.5191454181042116</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2773316772019603</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.1188790333326577</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.04339056641769333</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.02496902837454742</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.08294885925804485</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.05824419041574769</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.08937834520485273</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.02766133106619291</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.280554085961145</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.08484454530252006</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.1133443628907627</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.1241005857088528</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.02982513345676222</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.05788680263723674</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.1130418455220918</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1111120639927183</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.09855759559282742</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1207477986492186</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.00912079538591205</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.0813693175712514</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.0540124289549061</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1975404969883628</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.07982109192302066</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.02073396924641933</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.06329309576383095</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.08041025222081968</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.0268568656386304</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.0550253324327012</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.04359670920676496</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.05013198736437276</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.01336142295899115</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.006961048616991997</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.01249802592186753</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.005899383144940205</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1446168996258657</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1419693449424611</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0.0004515334052908549</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.04850484575129888</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.2021335913128045</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.07289011355661995</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1309518990581542</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.008538417899239708</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.02237659527608413</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.04848437542451323</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.03346134264582198</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.08115448268945702</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3969256418546411</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.01718061647502239</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.1595186744597766</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.4372282952607412</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.1139331941005722</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.1912269917031652</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1044942959889899</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.09466072415932646</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.02024099506776598</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.03685664010370459</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.2552359378293638</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.045977414084051</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.04261947115897059</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.03674726705645801</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.004084694325702766</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.4298116403776999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.266703631100383</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.1209157629426972</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.01793593956142691</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.006101564241852741</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.06069118740482153</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.05052678002126591</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.06157330246901688</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.01112595399125816</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.2414822798158145</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.05985773466473071</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.1240202384482711</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.1137540148714066</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.02917904079566028</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.05963678913299981</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.1147816444000389</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.1496826747591614</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.06868932225718427</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-0.1119537330061609</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0.01827083508161986</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.08222235311554203</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0.07805895886511502</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0.2053762820890815</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0.06667956780340208</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0.009997958543084565</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0.06021135600141588</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.04169724196238191</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>-0.005631911990851824</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>-0.03638945139055259</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0.01366938329681499</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0.05787979272810461</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.01772311591468043</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.002135051693077886</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0.03440564933223574</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0.01208967426754717</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0.1090035198219108</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0.1301528791426035</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.002589470299987057</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0.04926107642619053</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.1839387303034509</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0.07780575109705781</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0.1383156177246908</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0.002269034342212356</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>-0.009107064464106952</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>-0.03162385840654541</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>-0.040712622699525</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0.0758062636767521</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-0.2632674171497739</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.209488579268205</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6283093612791977</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.16441393391849</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3905909750829961</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.067381410106608</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.08536340758348407</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.02150163681497325</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.128464423379295</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.1540701535566233</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.02410445369008753</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.3189598640268801</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.08704243343982818</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.3521654900326996</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.02474078680267843</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.02157083022841234</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.2630871735945537</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.6539432702725795</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.1945146997898888</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.5691703431710214</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-0.3498127435036994</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.1527822424762326</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.03445941759659151</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0.02567225477356964</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.01203677852762843</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>-0.04024737753969684</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.3525289303833425</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.07345054580648686</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.04725116843565927</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-0.06039160539440133</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0.0775998314595973</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.19300799013398</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0.270372402189268</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0.08847749042046107</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.1431402407705024</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0.1493073813460601</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0.005702698874129549</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.1655221300707579</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-0.1487924714087882</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.02059958295346414</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.1345543001457302</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>-0.1932710553984657</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0.06870129930356661</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>-0.1085888242326713</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>-0.2807577804850698</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>-0.05828302996004474</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.1747669799486979</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>-0.06677483701364652</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0.02145072903661248</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>-0.09520561870017522</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>-0.1823384893688573</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>0.04976585726261427</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0.04071157965018422</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>-0.1488192175556596</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>-0.1582405464879239</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>-0.06669776593887092</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>-0.2664089717302998</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0.02585028793104953</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>0.001954674052398164</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>-0.09633217170277589</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>-0.1617989115940726</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>-0.09756517395285559</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG18" t="n">
         <v>0</v>
       </c>
     </row>
